--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260717.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260717.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>42,929,027</t>
+          <t>43,137,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>65.84%</t>
+          <t>65.93%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2,592,703</t>
+          <t>2,604,703</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.96%</t>
+          <t>5.86%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,502,000</t>
+          <t>21,606,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,842,267</t>
+          <t>5,870,267</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>20,540,286</t>
+          <t>20,639,286</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>512,000</t>
+          <t>514,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,772,608</t>
+          <t>2,786,608</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,322,901</t>
+          <t>2,333,901</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,654,285</t>
+          <t>4,676,285</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>563,222</t>
+          <t>566,222</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,447,296</t>
+          <t>5,473,296</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -880,46 +880,46 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2,009,288</t>
+          <t>1,194,617</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>1,188,617</t>
+          <t>2,018,288</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,317,520</t>
+          <t>5,342,520</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -963,56 +963,56 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,343,000</t>
+          <t>1,349,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>3,444,000</t>
+          <t>12,988,134</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>12,925,134</t>
+          <t>3,461,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>165,000</t>
+          <t>166,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1051,34 +1051,34 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>101,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>314,672</t>
+          <t>864,349</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>605,600</t>
+          <t>608,600</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1117,34 +1117,34 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,914,321</t>
+          <t>1,924,321</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>860,349</t>
+          <t>316,672</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1161,29 +1161,29 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>141,482</t>
+          <t>142,482</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>138,921</t>
+          <t>154,499</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>153,499</t>
+          <t>139,921</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,39 +1217,39 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>377,000</t>
+          <t>1,010,822</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,005,822</t>
+          <t>379,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>580,000</t>
+          <t>815,897</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,234,000</t>
+          <t>3,250,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>811,897</t>
+          <t>5,770,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,839,000</t>
+          <t>583,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,742,000</t>
+          <t>1,848,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,201,441</t>
+          <t>1,207,441</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>772,000</t>
+          <t>776,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>940,659</t>
+          <t>944,659</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>2,619,703</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1469,29 +1469,29 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,493,981</t>
+          <t>3,509,981</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>2,606,703</t>
+          <t>147,386</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>146,386</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>10,640,121</t>
+          <t>4,492,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,39 +1547,39 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,470,578</t>
+          <t>10,691,121</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,384,384</t>
+          <t>587,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>584,000</t>
+          <t>7,230,249</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,61 +1613,61 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,195,249</t>
+          <t>1,390,384</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,209,107</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,198,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>779,000</t>
+          <t>783,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>290,000</t>
+          <t>293,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>228,000</t>
+          <t>1,195,076</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,189,076</t>
+          <t>229,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,39 +1767,39 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>499,000</t>
+          <t>183,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>4,978,956</t>
+          <t>811,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>182,000</t>
+          <t>501,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,39 +1833,39 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>1,566,400</t>
+          <t>5,002,956</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>807,000</t>
+          <t>1,573,400</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>391,000</t>
+          <t>393,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>94,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>116,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,007,121</t>
+          <t>1,011,121</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>321,000</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>157,000</t>
+          <t>172,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>1,764,000</t>
+          <t>66,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>171,000</t>
+          <t>1,773,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>322,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>158,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>255,000</t>
+          <t>334,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>682,000</t>
+          <t>686,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>332,000</t>
+          <t>256,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>339,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>337,000</t>
+          <t>116,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>1,299,800,694</t>
+          <t>1,979,689,864</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>384,160,578</t>
+          <t>287,126,178</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>-885,233,431</t>
+          <t>-1,484,460,627</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
